--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486819_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486819_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.708</v>
+        <v>1.6268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8032</v>
+        <v>0.5481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9048</v>
+        <v>1.0786</v>
       </c>
       <c r="G2" t="n">
         <v>-1.6997</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0328</v>
+        <v>-0.0484</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1925</v>
+        <v>-0.0626</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1597</v>
+        <v>0.0142</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>V. DEL GROSSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2949</v>
+        <v>1.0464</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1321</v>
+        <v>0.2388</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8372000000000001</v>
+        <v>0.8076</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5493</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8274</v>
+        <v>-0.3519</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2781</v>
+        <v>-0.4883</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0677</v>
+        <v>-0.1706</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4144</v>
+        <v>-0.2136</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6534</v>
+        <v>0.043</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5184</v>
+        <v>-0.6697</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4131</v>
+        <v>-0.1384</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9314</v>
+        <v>-0.5313</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7031</v>
+        <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1419</v>
+        <v>-0.207</v>
       </c>
       <c r="T3" t="n">
-        <v>0.358</v>
+        <v>0.1238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7839</v>
+        <v>-0.3308</v>
       </c>
       <c r="V3" t="n">
-        <v>-4.1341</v>
+        <v>0.1628</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.8058</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. DEL GROSSO</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7347</v>
+        <v>0.5598</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0232</v>
+        <v>1.6702</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7579</v>
+        <v>-1.1104</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8401999999999999</v>
+        <v>2.5493</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3519</v>
+        <v>2.8274</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4883</v>
+        <v>-0.2781</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1706</v>
+        <v>3.0677</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2136</v>
+        <v>2.4144</v>
       </c>
       <c r="L4" t="n">
-        <v>0.043</v>
+        <v>0.6534</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6697</v>
+        <v>-0.5184</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1384</v>
+        <v>0.4131</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5313</v>
+        <v>-0.9314</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9308</v>
+        <v>2.7031</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5187</v>
+        <v>0.4068</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1383</v>
+        <v>-0.1039</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3805</v>
+        <v>0.5107</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1628</v>
+        <v>-4.1341</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>-0.3282</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1228</v>
+        <v>-3.8058</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1384</v>
+        <v>0.156</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1383</v>
+        <v>1.4534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001</v>
+        <v>-1.2975</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9858</v>
+        <v>0.1561</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0216</v>
+        <v>0.979</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0074</v>
+        <v>-0.8229</v>
       </c>
       <c r="J5" t="n">
-        <v>1.788</v>
+        <v>1.7707</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7811</v>
+        <v>1.1174</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0069</v>
+        <v>0.6534</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7738</v>
+        <v>-1.6146</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7594</v>
+        <v>-0.1384</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0143</v>
+        <v>-1.4763</v>
       </c>
       <c r="P5" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-3.8616</v>
-      </c>
       <c r="R5" t="n">
-        <v>2.8962</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3129</v>
+        <v>-0.3863</v>
       </c>
       <c r="T5" t="n">
-        <v>0.413</v>
+        <v>-0.5796</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8999</v>
+        <v>0.1933</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7766999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7989</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0222</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4563</v>
+        <v>-0.4317</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0398</v>
+        <v>1.7887</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4961</v>
+        <v>-2.2204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1561</v>
+        <v>-1.6632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.979</v>
+        <v>-2.034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8229</v>
+        <v>0.3708</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7707</v>
+        <v>0.0274</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1174</v>
+        <v>-1.6886</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6534</v>
+        <v>1.7159</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6146</v>
+        <v>-1.6906</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1384</v>
+        <v>-0.3454</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4763</v>
+        <v>-1.3451</v>
       </c>
       <c r="P6" t="n">
         <v>0.3862</v>
@@ -922,28 +922,28 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9986</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9933</v>
+        <v>-0.0142</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0053</v>
+        <v>-0.0825</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2277</v>
+        <v>2.741</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.9954</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5819</v>
+        <v>-0.2754</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4191</v>
+        <v>-0.72</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6632</v>
+        <v>-0.9858</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.034</v>
+        <v>1.0216</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3708</v>
+        <v>-2.0074</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0274</v>
+        <v>1.788</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6886</v>
+        <v>1.7811</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7159</v>
+        <v>0.0069</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6906</v>
+        <v>-2.7738</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3454</v>
+        <v>-0.7594</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3451</v>
+        <v>-2.0143</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3515</v>
+        <v>2.8962</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5022</v>
+        <v>0.1791</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2211</v>
+        <v>-0.0007</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2811</v>
+        <v>0.1798</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9421</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>2.741</v>
+        <v>1.7989</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7989</v>
+        <v>-1.0222</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5796</v>
+        <v>-2.0458</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4113</v>
+        <v>-1.1011</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1683</v>
+        <v>-0.9448</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1048</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5684</v>
+        <v>-0.0346</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5797</v>
+        <v>-0.2694</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0113</v>
+        <v>0.2348</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0648</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4779</v>
+        <v>-3.4061</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6275</v>
+        <v>-2.7792</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8504</v>
+        <v>-0.6269</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4558</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>0.066</v>
+        <v>0.1379</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3307</v>
+        <v>0.1791</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2647</v>
+        <v>-0.0412</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3505</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8563</v>
+        <v>-3.5654</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7806</v>
+        <v>-4.4151</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9242</v>
+        <v>0.8497</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7815</v>
@@ -1234,13 +1234,13 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>0.033</v>
+        <v>0.324</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3314</v>
+        <v>0.034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3645</v>
+        <v>0.29</v>
       </c>
       <c r="V10" t="n">
         <v>0.0852</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.331300000000001</v>
+        <v>-7.055399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1473</v>
+        <v>-2.8716</v>
       </c>
       <c r="F11" t="n">
         <v>-4.1841</v>
@@ -1285,7 +1285,7 @@
         <v>-12.9648</v>
       </c>
       <c r="J11" t="n">
-        <v>2.562799999999999</v>
+        <v>2.5628</v>
       </c>
       <c r="K11" t="n">
         <v>4.1447</v>
@@ -1297,7 +1297,7 @@
         <v>-11.3884</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.005399999999999849</v>
+        <v>-0.005399999999999905</v>
       </c>
       <c r="O11" t="n">
         <v>-11.3829</v>
@@ -1312,16 +1312,16 @@
         <v>18.3424</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.001299999999999996</v>
+        <v>0.2748000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9696</v>
+        <v>-0.6934999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>0.9683000000000002</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.297</v>
+        <v>-4.297000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>7.8095</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.6285</v>
+        <v>7.1415</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1248</v>
+        <v>6.0214</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5037</v>
+        <v>1.1201</v>
       </c>
       <c r="G12" t="n">
         <v>3.4385</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8665</v>
+        <v>0.3795</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1099</v>
+        <v>0.0065</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="V12" t="n">
         <v>4.8681</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5908</v>
+        <v>5.7068</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0209</v>
+        <v>4.814</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5699</v>
+        <v>0.8927</v>
       </c>
       <c r="G13" t="n">
         <v>5.7342</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0497</v>
+        <v>0.1656</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1927</v>
+        <v>-0.0141</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1431</v>
+        <v>0.1798</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0532</v>
+        <v>2.6988</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9952</v>
+        <v>0.478</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0581</v>
+        <v>2.2208</v>
       </c>
       <c r="G14" t="n">
         <v>2.2146</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9544</v>
+        <v>0.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7443</v>
+        <v>0.2272</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2101</v>
+        <v>0.3728</v>
       </c>
       <c r="V14" t="n">
         <v>0.6565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9761</v>
+        <v>2.6051</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4059</v>
+        <v>1.0957</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5702</v>
+        <v>1.5094</v>
       </c>
       <c r="G15" t="n">
         <v>2.1429</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>0.254</v>
+        <v>-0.1171</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2479</v>
+        <v>-0.0624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0061</v>
+        <v>-0.0547</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0095</v>
+        <v>0.9394</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2059</v>
+        <v>0.6196</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2154</v>
+        <v>0.3198</v>
       </c>
       <c r="G16" t="n">
         <v>1.4353</v>
@@ -1702,13 +1702,13 @@
         <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.197</v>
+        <v>-0.2481</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.2763</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5071</v>
+        <v>0.0281</v>
       </c>
       <c r="V16" t="n">
         <v>2.4554</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2041</v>
+        <v>-0.0469</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6466</v>
+        <v>0.8534</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8506</v>
+        <v>-0.9003</v>
       </c>
       <c r="G17" t="n">
         <v>3.5905</v>
@@ -1780,13 +1780,13 @@
         <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2813</v>
+        <v>-0.1241</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5243</v>
+        <v>-0.3174</v>
       </c>
       <c r="U17" t="n">
-        <v>0.243</v>
+        <v>0.1934</v>
       </c>
       <c r="V17" t="n">
         <v>-2.741</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2884</v>
+        <v>-1.2387</v>
       </c>
       <c r="E18" t="n">
         <v>-0.4386</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8498</v>
+        <v>-0.8001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.745</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2152</v>
+        <v>-0.1655</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3282</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9387</v>
+        <v>-2.5747</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9461</v>
+        <v>-3.5325</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0075</v>
+        <v>0.9578</v>
       </c>
       <c r="G19" t="n">
         <v>-3.4813</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0053</v>
+        <v>0.3587</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5795</v>
+        <v>-0.1658</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5245</v>
       </c>
       <c r="V19" t="n">
         <v>1.5133</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3357</v>
+        <v>-3.3676</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.157</v>
+        <v>-2.0536</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1788</v>
+        <v>-1.314</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5055</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3748</v>
+        <v>-0.4067</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4691</v>
+        <v>-0.3657</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.041</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1409</v>
+        <v>-3.843</v>
       </c>
       <c r="E21" t="n">
         <v>-3.6735</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4674</v>
+        <v>-0.1694</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9987</v>
@@ -2092,13 +2092,13 @@
         <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0497</v>
+        <v>0.2483</v>
       </c>
       <c r="T21" t="n">
         <v>0.11</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1597</v>
+        <v>0.1383</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8995</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7.331300000000001</v>
+        <v>8.020700000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>4.184099999999999</v>
+        <v>4.183900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>3.147400000000001</v>
+        <v>3.8368</v>
       </c>
       <c r="G22" t="n">
         <v>8.825500000000002</v>
@@ -2170,13 +2170,13 @@
         <v>12.5501</v>
       </c>
       <c r="S22" t="n">
-        <v>0.001300000000000155</v>
+        <v>0.6906000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9685</v>
+        <v>-0.9684</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9695000000000003</v>
+        <v>1.6591</v>
       </c>
       <c r="V22" t="n">
         <v>4.296900000000001</v>
